--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136921023</v>
       </c>
       <c r="B12" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136921023</v>
       </c>
       <c r="B12" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136921023</v>
       </c>
       <c r="B12" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136921023</v>
       </c>
       <c r="B12" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136921023</v>
       </c>
       <c r="B12" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29231-2026 artfynd.xlsx
+++ b/artfynd/A 29231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921026</v>
       </c>
       <c r="B2" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921040</v>
       </c>
       <c r="B3" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136921045</v>
       </c>
       <c r="B4" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136921041</v>
       </c>
       <c r="B5" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136921034</v>
       </c>
       <c r="B6" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>136921038</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>136921043</v>
       </c>
       <c r="B8" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136921037</v>
       </c>
       <c r="B9" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136921032</v>
       </c>
       <c r="B10" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136921033</v>
       </c>
       <c r="B11" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
